--- a/output/Tables/2019/cases_prev_2019_area.xlsx
+++ b/output/Tables/2019/cases_prev_2019_area.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -425,11 +425,6 @@
           <t>tot_soc_costs_up</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL_mixed</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -443,43 +438,40 @@
         </is>
       </c>
       <c r="C2">
-        <v>2996258.501017056</v>
+        <v>421214.3941698477</v>
       </c>
       <c r="D2">
-        <v>1950010.923785163</v>
+        <v>274975.6576435625</v>
       </c>
       <c r="E2">
-        <v>3924996.641465042</v>
+        <v>551108.2542967909</v>
       </c>
       <c r="F2">
-        <v>10607411.11575117</v>
+        <v>1463407.025029395</v>
       </c>
       <c r="G2">
-        <v>6424345.676545711</v>
+        <v>897665.1386404218</v>
       </c>
       <c r="H2">
-        <v>16482774.48202955</v>
+        <v>2254431.012678022</v>
       </c>
       <c r="I2">
-        <v>31139779758.09027</v>
+        <v>4516283293.639452</v>
       </c>
       <c r="J2">
-        <v>13395430955.84865</v>
+        <v>1991501365.785143</v>
       </c>
       <c r="K2">
-        <v>46537561292.98689</v>
+        <v>6709110501.833838</v>
       </c>
       <c r="L2">
-        <v>1410785678394.905</v>
+        <v>194633134328.9095</v>
       </c>
       <c r="M2">
-        <v>854437974980.5797</v>
+        <v>119389463439.1761</v>
       </c>
       <c r="N2">
-        <v>2192209006109.929</v>
-      </c>
-      <c r="O2">
-        <v>8802962.455957744</v>
+        <v>299839324686.1771</v>
       </c>
     </row>
     <row r="3">
@@ -494,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>1754297.842080659</v>
+        <v>240368.8630631386</v>
       </c>
       <c r="D3">
-        <v>1353754.866802891</v>
+        <v>185388.8581129597</v>
       </c>
       <c r="E3">
-        <v>2090106.81662704</v>
+        <v>286445.139676228</v>
       </c>
       <c r="F3">
-        <v>5054114.516026317</v>
+        <v>672362.6305331753</v>
       </c>
       <c r="G3">
-        <v>2415302.85023763</v>
+        <v>321118.1429979233</v>
       </c>
       <c r="H3">
-        <v>9198170.627208216</v>
+        <v>1223931.206653062</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -521,16 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>672197230631.5001</v>
+        <v>89424229860.91232</v>
       </c>
       <c r="M3">
-        <v>321235279081.6049</v>
+        <v>42708713018.7238</v>
       </c>
       <c r="N3">
-        <v>1223356693418.693</v>
-      </c>
-      <c r="O3">
-        <v>5175304.065828888</v>
+        <v>162782850484.8573</v>
       </c>
     </row>
     <row r="4">
@@ -545,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>376038.6355577886</v>
+        <v>56513.8995147949</v>
       </c>
       <c r="D4">
-        <v>324470.1610992159</v>
+        <v>48791.29002398933</v>
       </c>
       <c r="E4">
-        <v>424221.9654627933</v>
+        <v>63731.18949027691</v>
       </c>
       <c r="F4">
-        <v>4360855.108308602</v>
+        <v>626899.9917475552</v>
       </c>
       <c r="G4">
-        <v>3779012.297223494</v>
+        <v>543005.5653916668</v>
       </c>
       <c r="H4">
-        <v>4905479.777887893</v>
+        <v>705418.2365733559</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -572,16 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>579993729405.0441</v>
+        <v>83377698902.42484</v>
       </c>
       <c r="M4">
-        <v>502608635530.7247</v>
+        <v>72219740197.09169</v>
       </c>
       <c r="N4">
-        <v>652428810459.0897</v>
-      </c>
-      <c r="O4">
-        <v>1099960.105159259</v>
+        <v>93820625464.25633</v>
       </c>
     </row>
     <row r="5">
@@ -596,43 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>371238.7460536174</v>
+        <v>51293.52625405673</v>
       </c>
       <c r="D5">
-        <v>-20080.30315994376</v>
+        <v>-2716.803399319634</v>
       </c>
       <c r="E5">
-        <v>746578.13551673</v>
+        <v>103161.8119143068</v>
       </c>
       <c r="F5">
-        <v>577696.4053807557</v>
+        <v>76353.52739699572</v>
       </c>
       <c r="G5">
-        <v>-25690.59339465222</v>
+        <v>-3318.852566345327</v>
       </c>
       <c r="H5">
-        <v>1341431.305411289</v>
+        <v>177306.9710400286</v>
       </c>
       <c r="I5">
-        <v>5496932112.815964</v>
+        <v>759503243.2438169</v>
       </c>
       <c r="J5">
-        <v>-297329048.8892975</v>
+        <v>-40227707.93372593</v>
       </c>
       <c r="K5">
-        <v>11054582452.59606</v>
+        <v>1527516949.015147</v>
       </c>
       <c r="L5">
-        <v>76833621915.6405</v>
+        <v>10155019143.80043</v>
       </c>
       <c r="M5">
-        <v>-3416848921.488745</v>
+        <v>-441407391.3239285</v>
       </c>
       <c r="N5">
-        <v>178410363619.7014</v>
-      </c>
-      <c r="O5">
-        <v>1081448.414805525</v>
+        <v>23581827148.3238</v>
       </c>
     </row>
     <row r="6">
@@ -647,43 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>319022.624205747</v>
+        <v>47236.87893732829</v>
       </c>
       <c r="D6">
-        <v>224297.5274353438</v>
+        <v>33212.99389435949</v>
       </c>
       <c r="E6">
-        <v>403275.0368057017</v>
+        <v>59718.82797233685</v>
       </c>
       <c r="F6">
-        <v>298792.0730533701</v>
+        <v>42732.99898939581</v>
       </c>
       <c r="G6">
-        <v>166615.8285685381</v>
+        <v>23775.41224171267</v>
       </c>
       <c r="H6">
-        <v>457240.014836755</v>
+        <v>65495.49338728898</v>
       </c>
       <c r="I6">
-        <v>17770198213.50903</v>
+        <v>2631188630.567058</v>
       </c>
       <c r="J6">
-        <v>12493820873.20318</v>
+        <v>1850030185.90361</v>
       </c>
       <c r="K6">
-        <v>22463226100.15017</v>
+        <v>3326458155.715104</v>
       </c>
       <c r="L6">
-        <v>39739345716.09822</v>
+        <v>5683488865.589643</v>
       </c>
       <c r="M6">
-        <v>22159905199.61557</v>
+        <v>3162129828.147785</v>
       </c>
       <c r="N6">
-        <v>60812921973.28841</v>
-      </c>
-      <c r="O6">
-        <v>931010.4843306937</v>
+        <v>8710900620.509434</v>
       </c>
     </row>
     <row r="7">
@@ -698,43 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>91450.04186722104</v>
+        <v>13959.1961673284</v>
       </c>
       <c r="D7">
-        <v>66520.8961658714</v>
+        <v>10157.64026548246</v>
       </c>
       <c r="E7">
-        <v>112980.5788152436</v>
+        <v>17243.39989211399</v>
       </c>
       <c r="F7">
-        <v>149756.1096235288</v>
+        <v>22032.68308364361</v>
       </c>
       <c r="G7">
-        <v>87513.04566146016</v>
+        <v>12872.55829590665</v>
       </c>
       <c r="H7">
-        <v>210375.9675137345</v>
+        <v>30959.63200922539</v>
       </c>
       <c r="I7">
-        <v>1539927255.002139</v>
+        <v>235058904.2616436</v>
       </c>
       <c r="J7">
-        <v>1120145370.537098</v>
+        <v>171044504.4304591</v>
       </c>
       <c r="K7">
-        <v>1902479966.669878</v>
+        <v>290361610.7833073</v>
       </c>
       <c r="L7">
-        <v>19917562579.92933</v>
+        <v>2930346850.1246</v>
       </c>
       <c r="M7">
-        <v>11639235072.9742</v>
+        <v>1712050253.355584</v>
       </c>
       <c r="N7">
-        <v>27980003679.32669</v>
-      </c>
-      <c r="O7">
-        <v>264099.2676299961</v>
+        <v>4117631057.226976</v>
       </c>
     </row>
     <row r="8">
@@ -749,43 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>84210.61125202276</v>
+        <v>11842.03023320078</v>
       </c>
       <c r="D8">
-        <v>1047.775441784852</v>
+        <v>141.6787460911411</v>
       </c>
       <c r="E8">
-        <v>147834.1082375328</v>
+        <v>20807.88535152832</v>
       </c>
       <c r="F8">
-        <v>166196.903358591</v>
+        <v>23025.19327862965</v>
       </c>
       <c r="G8">
-        <v>1592.248249241332</v>
+        <v>212.3122795577478</v>
       </c>
       <c r="H8">
-        <v>370076.7891716578</v>
+        <v>51319.47301506125</v>
       </c>
       <c r="I8">
-        <v>6332722176.763141</v>
+        <v>890532515.5669334</v>
       </c>
       <c r="J8">
-        <v>78793760.99766222</v>
+        <v>10654383.38479992</v>
       </c>
       <c r="K8">
-        <v>11117272773.57078</v>
+        <v>1564773786.32028</v>
       </c>
       <c r="L8">
-        <v>22104188146.6926</v>
+        <v>3062350706.057743</v>
       </c>
       <c r="M8">
-        <v>211769017.1490971</v>
+        <v>28237533.18118046</v>
       </c>
       <c r="N8">
-        <v>49220212959.83048</v>
-      </c>
-      <c r="O8">
-        <v>251140.1182033821</v>
+        <v>6825489911.003146</v>
       </c>
     </row>
     <row r="9">
@@ -800,43 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>2927867.859763029</v>
+        <v>405569.5486771298</v>
       </c>
       <c r="D9">
-        <v>1903436.805819138</v>
+        <v>264544.9892755263</v>
       </c>
       <c r="E9">
-        <v>3836798.691488741</v>
+        <v>530754.9676267686</v>
       </c>
       <c r="F9">
-        <v>10391817.52527014</v>
+        <v>1410603.46417355</v>
       </c>
       <c r="G9">
-        <v>6339375.695540168</v>
+        <v>867351.2949004002</v>
       </c>
       <c r="H9">
-        <v>16067365.74002285</v>
+        <v>2169487.215998353</v>
       </c>
       <c r="I9">
-        <v>30681616761.12577</v>
+        <v>4353033041.809611</v>
       </c>
       <c r="J9">
-        <v>13178443724.02418</v>
+        <v>1912735811.523089</v>
       </c>
       <c r="K9">
-        <v>45815265620.0088</v>
+        <v>6464836695.780928</v>
       </c>
       <c r="L9">
-        <v>1382111730860.928</v>
+        <v>187610260735.0822</v>
       </c>
       <c r="M9">
-        <v>843136967506.8425</v>
+        <v>115357722221.7532</v>
       </c>
       <c r="N9">
-        <v>2136959643423.038</v>
-      </c>
-      <c r="O9">
-        <v>8802962.455957744</v>
+        <v>288541799727.781</v>
       </c>
     </row>
     <row r="10">
@@ -851,22 +822,22 @@
         </is>
       </c>
       <c r="C10">
-        <v>1713492.674707882</v>
+        <v>231716.1558831894</v>
       </c>
       <c r="D10">
-        <v>1324448.201868543</v>
+        <v>179051.8827354544</v>
       </c>
       <c r="E10">
-        <v>2040263.003454514</v>
+        <v>275934.5064710245</v>
       </c>
       <c r="F10">
-        <v>4844584.628102754</v>
+        <v>643756.1284944944</v>
       </c>
       <c r="G10">
-        <v>2318255.507636364</v>
+        <v>307981.8178954474</v>
       </c>
       <c r="H10">
-        <v>8811716.067919999</v>
+        <v>1171002.773335992</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -878,22 +849,19 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>644329755537.6663</v>
+        <v>85619565089.76775</v>
       </c>
       <c r="M10">
-        <v>308327982515.6364</v>
+        <v>40961581780.0945</v>
       </c>
       <c r="N10">
-        <v>1171958237033.36</v>
-      </c>
-      <c r="O10">
-        <v>5175304.065828888</v>
+        <v>155743368853.687</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>mort</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -902,49 +870,46 @@
         </is>
       </c>
       <c r="C11">
-        <v>367467.3430226314</v>
+        <v>53978.99272727947</v>
       </c>
       <c r="D11">
-        <v>-20958.40165485925</v>
+        <v>46708.48497474167</v>
       </c>
       <c r="E11">
-        <v>739118.5215499988</v>
+        <v>60786.27397847559</v>
       </c>
       <c r="F11">
-        <v>565247.958268129</v>
+        <v>607383.9142757314</v>
       </c>
       <c r="G11">
-        <v>-26554.23039671536</v>
+        <v>527101.4735638894</v>
       </c>
       <c r="H11">
-        <v>1312708.509450107</v>
+        <v>682634.4046139821</v>
       </c>
       <c r="I11">
-        <v>5441088948.136</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>-310331053.3034968</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>10944127948.59062</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>75177978449.66116</v>
+        <v>80782060598.67229</v>
       </c>
       <c r="M11">
-        <v>-3531712642.763143</v>
+        <v>70104495983.99728</v>
       </c>
       <c r="N11">
-        <v>174590231756.8643</v>
-      </c>
-      <c r="O11">
-        <v>1081448.414805525</v>
+        <v>90790375813.65962</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mort</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -953,43 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>363426.7907762225</v>
+        <v>50097.17071623793</v>
       </c>
       <c r="D12">
-        <v>314454.4921615712</v>
+        <v>-2820.101415203864</v>
       </c>
       <c r="E12">
-        <v>409278.1810317715</v>
+        <v>100762.5465009056</v>
       </c>
       <c r="F12">
-        <v>4369763.501031066</v>
+        <v>74619.37445955064</v>
       </c>
       <c r="G12">
-        <v>3791901.581066091</v>
+        <v>-3469.947666282956</v>
       </c>
       <c r="H12">
-        <v>4911462.932645921</v>
+        <v>173288.7035031838</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>741788806.7953339</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>-41757241.65492348</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1491991026.038915</v>
       </c>
       <c r="L12">
-        <v>581178545637.1318</v>
+        <v>9924376803.120235</v>
       </c>
       <c r="M12">
-        <v>504322910281.7901</v>
+        <v>-461503039.6156332</v>
       </c>
       <c r="N12">
-        <v>653224570041.9075</v>
-      </c>
-      <c r="O12">
-        <v>1099960.105159259</v>
+        <v>23047397565.92344</v>
       </c>
     </row>
     <row r="13">
@@ -1004,43 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>312425.3169169941</v>
+        <v>45191.80900532119</v>
       </c>
       <c r="D13">
-        <v>221703.3066203779</v>
+        <v>32037.13558413629</v>
       </c>
       <c r="E13">
-        <v>392887.5860253912</v>
+        <v>56868.77249776782</v>
       </c>
       <c r="F13">
-        <v>298719.8943432573</v>
+        <v>41571.96095689302</v>
       </c>
       <c r="G13">
-        <v>167727.5312958201</v>
+        <v>23318.47963966112</v>
       </c>
       <c r="H13">
-        <v>455359.9934114508</v>
+        <v>63409.8285206935</v>
       </c>
       <c r="I13">
-        <v>17402715002.91086</v>
+        <v>2517274145.214404</v>
       </c>
       <c r="J13">
-        <v>12349317585.36839</v>
+        <v>1784532526.307562</v>
       </c>
       <c r="K13">
-        <v>21884624316.78649</v>
+        <v>3167704365.670654</v>
       </c>
       <c r="L13">
-        <v>39729745947.65322</v>
+        <v>5529070807.266772</v>
       </c>
       <c r="M13">
-        <v>22307761662.34407</v>
+        <v>3101357792.074929</v>
       </c>
       <c r="N13">
-        <v>60562879123.72296</v>
-      </c>
-      <c r="O13">
-        <v>931010.4843306937</v>
+        <v>8433507193.252236</v>
       </c>
     </row>
     <row r="14">
@@ -1055,43 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>86113.38658665838</v>
+        <v>12934.41118488275</v>
       </c>
       <c r="D14">
-        <v>62670.1441070404</v>
+        <v>9415.914686372307</v>
       </c>
       <c r="E14">
-        <v>106381.6718701005</v>
+        <v>15975.9909843251</v>
       </c>
       <c r="F14">
-        <v>147859.5373990691</v>
+        <v>20869.11905234802</v>
       </c>
       <c r="G14">
-        <v>86368.16385021848</v>
+        <v>12194.97151108709</v>
       </c>
       <c r="H14">
-        <v>207828.1071835931</v>
+        <v>29325.37992707074</v>
       </c>
       <c r="I14">
-        <v>1450063316.732738</v>
+        <v>217802549.9422402</v>
       </c>
       <c r="J14">
-        <v>1055302556.618442</v>
+        <v>158554587.4038234</v>
       </c>
       <c r="K14">
-        <v>1791360972.620596</v>
+        <v>269019712.1850498</v>
       </c>
       <c r="L14">
-        <v>19665318474.07619</v>
+        <v>2775592833.962287</v>
       </c>
       <c r="M14">
-        <v>11486965792.07906</v>
+        <v>1621931210.974584</v>
       </c>
       <c r="N14">
-        <v>27641138255.41788</v>
-      </c>
-      <c r="O14">
-        <v>264099.2676299961</v>
+        <v>3900275530.300409</v>
       </c>
     </row>
     <row r="15">
@@ -1106,43 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>84942.34775264027</v>
+        <v>11651.00916021903</v>
       </c>
       <c r="D15">
-        <v>1119.062716464529</v>
+        <v>151.672710025489</v>
       </c>
       <c r="E15">
-        <v>148869.7275569654</v>
+        <v>20426.8771942701</v>
       </c>
       <c r="F15">
-        <v>165642.0061258619</v>
+        <v>22402.96693453318</v>
       </c>
       <c r="G15">
-        <v>1677.142088390434</v>
+        <v>224.4999565980998</v>
       </c>
       <c r="H15">
-        <v>368290.1294117735</v>
+        <v>49826.12609743083</v>
       </c>
       <c r="I15">
-        <v>6387749493.346173</v>
+        <v>876167539.8576332</v>
       </c>
       <c r="J15">
-        <v>84154635.34084746</v>
+        <v>11405939.46662686</v>
       </c>
       <c r="K15">
-        <v>11195152382.0111</v>
+        <v>1536121591.886309</v>
       </c>
       <c r="L15">
-        <v>22030386814.73963</v>
+        <v>2979594602.292913</v>
       </c>
       <c r="M15">
-        <v>223059897.7559277</v>
+        <v>29858494.22754727</v>
       </c>
       <c r="N15">
-        <v>48982587211.76588</v>
-      </c>
-      <c r="O15">
-        <v>251140.1182033821</v>
+        <v>6626874770.958301</v>
       </c>
     </row>
     <row r="16">
@@ -1157,43 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>2878836.095177522</v>
+        <v>360725.7794256359</v>
       </c>
       <c r="D16">
-        <v>1875769.817870131</v>
+        <v>235681.2757739804</v>
       </c>
       <c r="E16">
-        <v>3771007.967426852</v>
+        <v>472127.8975950318</v>
       </c>
       <c r="F16">
-        <v>10641971.71082468</v>
+        <v>1322779.76793264</v>
       </c>
       <c r="G16">
-        <v>6455055.038098364</v>
+        <v>807323.9331739176</v>
       </c>
       <c r="H16">
-        <v>16526534.28609488</v>
+        <v>2046306.942823823</v>
       </c>
       <c r="I16">
-        <v>29383911753.63067</v>
+        <v>3732821445.353777</v>
       </c>
       <c r="J16">
-        <v>12414866519.84773</v>
+        <v>1600831949.937253</v>
       </c>
       <c r="K16">
-        <v>44248742232.76902</v>
+        <v>5606158752.723078</v>
       </c>
       <c r="L16">
-        <v>1415382237539.682</v>
+        <v>175929709135.0412</v>
       </c>
       <c r="M16">
-        <v>858522320067.0824</v>
+        <v>107374083112.131</v>
       </c>
       <c r="N16">
-        <v>2198029060050.62</v>
-      </c>
-      <c r="O16">
-        <v>8802962.455957744</v>
+        <v>272158823395.5685</v>
       </c>
     </row>
     <row r="17">
@@ -1208,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>1707513.549040269</v>
+        <v>210437.8905157994</v>
       </c>
       <c r="D17">
-        <v>1311022.311871102</v>
+        <v>161461.0198051779</v>
       </c>
       <c r="E17">
-        <v>2038107.834854722</v>
+        <v>251275.0084889801</v>
       </c>
       <c r="F17">
-        <v>5058444.017979853</v>
+        <v>619284.1380716657</v>
       </c>
       <c r="G17">
-        <v>2403550.113850366</v>
+        <v>294078.6896811156</v>
       </c>
       <c r="H17">
-        <v>9224357.954415316</v>
+        <v>1129681.966296552</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1235,16 +1185,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>672773054391.3204</v>
+        <v>82364790363.53154</v>
       </c>
       <c r="M17">
-        <v>319672165142.0987</v>
+        <v>39112465727.58837</v>
       </c>
       <c r="N17">
-        <v>1226839607937.237</v>
-      </c>
-      <c r="O17">
-        <v>5175304.065828888</v>
+        <v>150247701517.4414</v>
       </c>
     </row>
     <row r="18">
@@ -1259,22 +1206,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>360494.6788252088</v>
+        <v>47782.13973022057</v>
       </c>
       <c r="D18">
-        <v>309785.9782212731</v>
+        <v>41037.36682772607</v>
       </c>
       <c r="E18">
-        <v>407844.3234837536</v>
+        <v>54080.52586579061</v>
       </c>
       <c r="F18">
-        <v>4431683.996164855</v>
+        <v>561419.5865093252</v>
       </c>
       <c r="G18">
-        <v>3826665.499957789</v>
+        <v>484747.8274755173</v>
       </c>
       <c r="H18">
-        <v>4997708.633558544</v>
+        <v>633176.436107637</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1286,16 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>589413971489.9257</v>
+        <v>74668805005.74025</v>
       </c>
       <c r="M18">
-        <v>508946511494.386</v>
+        <v>64471461054.2438</v>
       </c>
       <c r="N18">
-        <v>664695248263.2864</v>
-      </c>
-      <c r="O18">
-        <v>1099960.105159259</v>
+        <v>84212466002.31572</v>
       </c>
     </row>
     <row r="19">
@@ -1310,43 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>342742.32572928</v>
+        <v>42258.68551835822</v>
       </c>
       <c r="D19">
-        <v>-15612.56933581101</v>
+        <v>-1833.904308357241</v>
       </c>
       <c r="E19">
-        <v>689989.100975584</v>
+        <v>85089.41198710834</v>
       </c>
       <c r="F19">
-        <v>547691.3007433313</v>
+        <v>66415.44239852291</v>
       </c>
       <c r="G19">
-        <v>-20489.17472765285</v>
+        <v>-2385.865331223808</v>
       </c>
       <c r="H19">
-        <v>1273082.916794532</v>
+        <v>154411.6513993545</v>
       </c>
       <c r="I19">
-        <v>5074985617.073461</v>
+        <v>625724356.4703307</v>
       </c>
       <c r="J19">
-        <v>-231175314.1553495</v>
+        <v>-27154621.09384565</v>
       </c>
       <c r="K19">
-        <v>10216668618.14554</v>
+        <v>1259918923.293112</v>
       </c>
       <c r="L19">
-        <v>72842942998.86307</v>
+        <v>8833253839.003548</v>
       </c>
       <c r="M19">
-        <v>-2725060238.777829</v>
+        <v>-317320089.0527664</v>
       </c>
       <c r="N19">
-        <v>169320027933.6727</v>
-      </c>
-      <c r="O19">
-        <v>1081448.414805525</v>
+        <v>20536749636.11415</v>
       </c>
     </row>
     <row r="20">
@@ -1361,43 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>299562.5432079196</v>
+        <v>38574.49935164709</v>
       </c>
       <c r="D20">
-        <v>207023.1659451912</v>
+        <v>26586.4373874868</v>
       </c>
       <c r="E20">
-        <v>383107.951288586</v>
+        <v>49448.46981781944</v>
       </c>
       <c r="F20">
-        <v>291635.7207593407</v>
+        <v>36652.39340397252</v>
       </c>
       <c r="G20">
-        <v>159830.3225273005</v>
+        <v>20047.59142403122</v>
       </c>
       <c r="H20">
-        <v>451522.268365657</v>
+        <v>56849.12169021871</v>
       </c>
       <c r="I20">
-        <v>16686232781.7674</v>
+        <v>2148676762.885436</v>
       </c>
       <c r="J20">
-        <v>11531604389.47893</v>
+        <v>1480917735.357788</v>
       </c>
       <c r="K20">
-        <v>21339879102.67714</v>
+        <v>2754378665.792172</v>
       </c>
       <c r="L20">
-        <v>38787550860.99232</v>
+        <v>4874768322.728345</v>
       </c>
       <c r="M20">
-        <v>21257432896.13096</v>
+        <v>2666329659.396152</v>
       </c>
       <c r="N20">
-        <v>60052461692.63238</v>
-      </c>
-      <c r="O20">
-        <v>931010.4843306937</v>
+        <v>7560933184.799088</v>
       </c>
     </row>
     <row r="21">
@@ -1412,43 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>86535.83917612291</v>
+        <v>11503.68703349809</v>
       </c>
       <c r="D21">
-        <v>62791.8188250727</v>
+        <v>8342.797891455983</v>
       </c>
       <c r="E21">
-        <v>107182.0013020493</v>
+        <v>14259.34811659477</v>
       </c>
       <c r="F21">
-        <v>144654.1935770974</v>
+        <v>18364.80374344331</v>
       </c>
       <c r="G21">
-        <v>84302.98575235681</v>
+        <v>10699.91313891912</v>
       </c>
       <c r="H21">
-        <v>203733.526635085</v>
+        <v>25879.40465696505</v>
       </c>
       <c r="I21">
-        <v>1457176995.886772</v>
+        <v>193710585.9570748</v>
       </c>
       <c r="J21">
-        <v>1057351437.195413</v>
+        <v>140484373.6942273</v>
       </c>
       <c r="K21">
-        <v>1804837719.925234</v>
+        <v>240113162.9353394</v>
       </c>
       <c r="L21">
-        <v>19239007745.75396</v>
+        <v>2442518897.877961</v>
       </c>
       <c r="M21">
-        <v>11212297105.06346</v>
+        <v>1423088447.476243</v>
       </c>
       <c r="N21">
-        <v>27096559042.4663</v>
-      </c>
-      <c r="O21">
-        <v>264099.2676299961</v>
+        <v>3441960819.376352</v>
       </c>
     </row>
     <row r="22">
@@ -1463,43 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>81987.15919872132</v>
+        <v>10168.87727611247</v>
       </c>
       <c r="D22">
-        <v>759.1123433032037</v>
+        <v>87.55817049086444</v>
       </c>
       <c r="E22">
-        <v>144776.7555221561</v>
+        <v>17975.13331873855</v>
       </c>
       <c r="F22">
-        <v>167862.4816001979</v>
+        <v>20643.40380571091</v>
       </c>
       <c r="G22">
-        <v>1195.290738204483</v>
+        <v>135.7767855582018</v>
       </c>
       <c r="H22">
-        <v>376128.9863257522</v>
+        <v>46308.36267309635</v>
       </c>
       <c r="I22">
-        <v>6165516358.903033</v>
+        <v>764709740.0409356</v>
       </c>
       <c r="J22">
-        <v>57086007.3287445</v>
+        <v>6584461.979083515</v>
       </c>
       <c r="K22">
-        <v>10887356792.0211</v>
+        <v>1351748000.702454</v>
       </c>
       <c r="L22">
-        <v>22325710052.82632</v>
+        <v>2745572706.159552</v>
       </c>
       <c r="M22">
-        <v>158973668.1811962</v>
+        <v>18058312.47924083</v>
       </c>
       <c r="N22">
-        <v>50025155181.32504</v>
-      </c>
-      <c r="O22">
-        <v>251140.1182033821</v>
+        <v>6159012235.521814</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019_area.xlsx
+++ b/output/Tables/2019/cases_prev_2019_area.xlsx
@@ -438,40 +438,40 @@
         </is>
       </c>
       <c r="C2">
-        <v>421214.3941698477</v>
+        <v>2894762.809937084</v>
       </c>
       <c r="D2">
-        <v>274975.6576435625</v>
+        <v>1848107.818410433</v>
       </c>
       <c r="E2">
-        <v>551108.2542967909</v>
+        <v>3788140.850758359</v>
       </c>
       <c r="F2">
-        <v>1463407.025029395</v>
+        <v>7889762.712992449</v>
       </c>
       <c r="G2">
-        <v>897665.1386404218</v>
+        <v>3902046.741541974</v>
       </c>
       <c r="H2">
-        <v>2254431.012678022</v>
+        <v>13226700.51329626</v>
       </c>
       <c r="I2">
-        <v>4516283293.639452</v>
+        <v>39187854541.78131</v>
       </c>
       <c r="J2">
-        <v>1991501365.785143</v>
+        <v>25023131775.73364</v>
       </c>
       <c r="K2">
-        <v>6709110501.833838</v>
+        <v>51286936575.69694</v>
       </c>
       <c r="L2">
-        <v>194633134328.9095</v>
+        <v>1049338440827.996</v>
       </c>
       <c r="M2">
-        <v>119389463439.1761</v>
+        <v>518972216625.0825</v>
       </c>
       <c r="N2">
-        <v>299839324686.1771</v>
+        <v>1759151168268.403</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>240368.8630631386</v>
+        <v>1282525.778235175</v>
       </c>
       <c r="D3">
-        <v>185388.8581129597</v>
+        <v>818572.715849875</v>
       </c>
       <c r="E3">
-        <v>286445.139676228</v>
+        <v>1678081.630463409</v>
       </c>
       <c r="F3">
-        <v>672362.6305331753</v>
+        <v>3564716.970122794</v>
       </c>
       <c r="G3">
-        <v>321118.1429979233</v>
+        <v>1406932.6904066</v>
       </c>
       <c r="H3">
-        <v>1223931.206653062</v>
+        <v>7125371.754365409</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,19 +513,19 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>89424229860.91232</v>
+        <v>474107357026.3315</v>
       </c>
       <c r="M3">
-        <v>42708713018.7238</v>
+        <v>187122047824.0778</v>
       </c>
       <c r="N3">
-        <v>162782850484.8573</v>
+        <v>947674443330.5994</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mort</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,46 +534,46 @@
         </is>
       </c>
       <c r="C4">
-        <v>56513.8995147949</v>
+        <v>936181.8281366293</v>
       </c>
       <c r="D4">
-        <v>48791.29002398933</v>
+        <v>597613.1732159001</v>
       </c>
       <c r="E4">
-        <v>63731.18949027691</v>
+        <v>1225018.997874267</v>
       </c>
       <c r="F4">
-        <v>626899.9917475552</v>
+        <v>1382824.412304197</v>
       </c>
       <c r="G4">
-        <v>543005.5653916668</v>
+        <v>698105.1481779148</v>
       </c>
       <c r="H4">
-        <v>705418.2365733559</v>
+        <v>2088871.886616091</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>13862044329.21922</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>8848858255.807821</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>18138856301.52413</v>
       </c>
       <c r="L4">
-        <v>83377698902.42484</v>
+        <v>183915646836.4582</v>
       </c>
       <c r="M4">
-        <v>72219740197.09169</v>
+        <v>92847984707.66267</v>
       </c>
       <c r="N4">
-        <v>93820625464.25633</v>
+        <v>277819960919.9401</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -582,46 +582,46 @@
         </is>
       </c>
       <c r="C5">
-        <v>51293.52625405673</v>
+        <v>307005.7300699163</v>
       </c>
       <c r="D5">
-        <v>-2716.803399319634</v>
+        <v>196118.0198012635</v>
       </c>
       <c r="E5">
-        <v>103161.8119143068</v>
+        <v>401902.073981562</v>
       </c>
       <c r="F5">
-        <v>76353.52739699572</v>
+        <v>278572.7295096618</v>
       </c>
       <c r="G5">
-        <v>-3318.852566345327</v>
+        <v>139564.8094474466</v>
       </c>
       <c r="H5">
-        <v>177306.9710400286</v>
+        <v>444304.7376784908</v>
       </c>
       <c r="I5">
-        <v>759503243.2438169</v>
+        <v>17100833176.35455</v>
       </c>
       <c r="J5">
-        <v>-40227707.93372593</v>
+        <v>10924165938.96986</v>
       </c>
       <c r="K5">
-        <v>1527516949.015147</v>
+        <v>22386749324.92086</v>
       </c>
       <c r="L5">
-        <v>10155019143.80043</v>
+        <v>37050173024.78503</v>
       </c>
       <c r="M5">
-        <v>-441407391.3239285</v>
+        <v>18562119656.5104</v>
       </c>
       <c r="N5">
-        <v>23581827148.3238</v>
+        <v>59092530111.23927</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>mort</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,46 +630,46 @@
         </is>
       </c>
       <c r="C6">
-        <v>47236.87893732829</v>
+        <v>210769.2408234931</v>
       </c>
       <c r="D6">
-        <v>33212.99389435949</v>
+        <v>134717.4247567642</v>
       </c>
       <c r="E6">
-        <v>59718.82797233685</v>
+        <v>275966.008562903</v>
       </c>
       <c r="F6">
-        <v>42732.99898939581</v>
+        <v>2378994.283106449</v>
       </c>
       <c r="G6">
-        <v>23775.41224171267</v>
+        <v>1518537.400400387</v>
       </c>
       <c r="H6">
-        <v>65495.49338728898</v>
+        <v>3112452.688807989</v>
       </c>
       <c r="I6">
-        <v>2631188630.567058</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>1850030185.90361</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>3326458155.715104</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>5683488865.589643</v>
+        <v>316406239653.1577</v>
       </c>
       <c r="M6">
-        <v>3162129828.147785</v>
+        <v>201965474253.2515</v>
       </c>
       <c r="N6">
-        <v>8710900620.509434</v>
+        <v>413956207611.4626</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -678,46 +678,46 @@
         </is>
       </c>
       <c r="C7">
-        <v>13959.1961673284</v>
+        <v>95262.26308635654</v>
       </c>
       <c r="D7">
-        <v>10157.64026548246</v>
+        <v>60791.47842147082</v>
       </c>
       <c r="E7">
-        <v>17243.39989211399</v>
+        <v>124614.6342804619</v>
       </c>
       <c r="F7">
-        <v>22032.68308364361</v>
+        <v>184422.1113187462</v>
       </c>
       <c r="G7">
-        <v>12872.55829590665</v>
+        <v>87566.05762275173</v>
       </c>
       <c r="H7">
-        <v>30959.63200922539</v>
+        <v>306250.8394600226</v>
       </c>
       <c r="I7">
-        <v>235058904.2616436</v>
+        <v>7163817446.357061</v>
       </c>
       <c r="J7">
-        <v>171044504.4304591</v>
+        <v>4571579968.773042</v>
       </c>
       <c r="K7">
-        <v>290361610.7833073</v>
+        <v>9371145112.525038</v>
       </c>
       <c r="L7">
-        <v>2930346850.1246</v>
+        <v>24528140805.39325</v>
       </c>
       <c r="M7">
-        <v>1712050253.355584</v>
+        <v>11646285663.82598</v>
       </c>
       <c r="N7">
-        <v>4117631057.226976</v>
+        <v>40731361648.183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>11842.03023320078</v>
+        <v>63017.96958551427</v>
       </c>
       <c r="D8">
-        <v>141.6787460911411</v>
+        <v>40295.00636515921</v>
       </c>
       <c r="E8">
-        <v>20807.88535152832</v>
+        <v>82557.50559575506</v>
       </c>
       <c r="F8">
-        <v>23025.19327862965</v>
+        <v>100232.2066306015</v>
       </c>
       <c r="G8">
-        <v>212.3122795577478</v>
+        <v>51340.63548687388</v>
       </c>
       <c r="H8">
-        <v>51319.47301506125</v>
+        <v>149448.6063682592</v>
       </c>
       <c r="I8">
-        <v>890532515.5669334</v>
+        <v>1061159589.850477</v>
       </c>
       <c r="J8">
-        <v>10654383.38479992</v>
+        <v>678527612.1829165</v>
       </c>
       <c r="K8">
-        <v>1564773786.32028</v>
+        <v>1390185836.726909</v>
       </c>
       <c r="L8">
-        <v>3062350706.057743</v>
+        <v>13330883481.87</v>
       </c>
       <c r="M8">
-        <v>28237533.18118046</v>
+        <v>6828304519.754226</v>
       </c>
       <c r="N8">
-        <v>6825489911.003146</v>
+        <v>19876664646.97848</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>405569.5486771298</v>
+        <v>2775401.592423047</v>
       </c>
       <c r="D9">
-        <v>264544.9892755263</v>
+        <v>1771926.780446545</v>
       </c>
       <c r="E9">
-        <v>530754.9676267686</v>
+        <v>3629675.923693352</v>
       </c>
       <c r="F9">
-        <v>1410603.46417355</v>
+        <v>7568830.837991592</v>
       </c>
       <c r="G9">
-        <v>867351.2949004002</v>
+        <v>3751531.470255754</v>
       </c>
       <c r="H9">
-        <v>2169487.215998353</v>
+        <v>12654421.21214452</v>
       </c>
       <c r="I9">
-        <v>4353033041.809611</v>
+        <v>37801260758.09966</v>
       </c>
       <c r="J9">
-        <v>1912735811.523089</v>
+        <v>24142630787.81494</v>
       </c>
       <c r="K9">
-        <v>6464836695.780928</v>
+        <v>49441315001.58229</v>
       </c>
       <c r="L9">
-        <v>187610260735.0822</v>
+        <v>1006654501452.882</v>
       </c>
       <c r="M9">
-        <v>115357722221.7532</v>
+        <v>498953685544.0153</v>
       </c>
       <c r="N9">
-        <v>288541799727.781</v>
+        <v>1683038021215.221</v>
       </c>
     </row>
     <row r="10">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C10">
-        <v>231716.1558831894</v>
+        <v>1222367.374760105</v>
       </c>
       <c r="D10">
-        <v>179051.8827354544</v>
+        <v>780052.806066409</v>
       </c>
       <c r="E10">
-        <v>275934.5064710245</v>
+        <v>1598378.627405813</v>
       </c>
       <c r="F10">
-        <v>643756.1284944944</v>
+        <v>3375300.822845115</v>
       </c>
       <c r="G10">
-        <v>307981.8178954474</v>
+        <v>1331617.897367873</v>
       </c>
       <c r="H10">
-        <v>1171002.773335992</v>
+        <v>6743203.258185442</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -849,19 +849,19 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>85619565089.76775</v>
+        <v>448915009438.4003</v>
       </c>
       <c r="M10">
-        <v>40961581780.0945</v>
+        <v>177105180349.9272</v>
       </c>
       <c r="N10">
-        <v>155743368853.687</v>
+        <v>896846033338.6637</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mort</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -870,46 +870,46 @@
         </is>
       </c>
       <c r="C11">
-        <v>53978.99272727947</v>
+        <v>903896.9432947705</v>
       </c>
       <c r="D11">
-        <v>46708.48497474167</v>
+        <v>577016.7305555792</v>
       </c>
       <c r="E11">
-        <v>60786.27397847559</v>
+        <v>1182059.100727383</v>
       </c>
       <c r="F11">
-        <v>607383.9142757314</v>
+        <v>1334026.49933925</v>
       </c>
       <c r="G11">
-        <v>527101.4735638894</v>
+        <v>673255.3169188456</v>
       </c>
       <c r="H11">
-        <v>682634.4046139821</v>
+        <v>2013980.005359921</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>13384002039.36579</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>8543886729.336502</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>17502749104.47045</v>
       </c>
       <c r="L11">
-        <v>80782060598.67229</v>
+        <v>177425524412.1203</v>
       </c>
       <c r="M11">
-        <v>70104495983.99728</v>
+        <v>89542957150.20647</v>
       </c>
       <c r="N11">
-        <v>90790375813.65962</v>
+        <v>267859340712.8694</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -918,46 +918,46 @@
         </is>
       </c>
       <c r="C12">
-        <v>50097.17071623793</v>
+        <v>295218.8548246627</v>
       </c>
       <c r="D12">
-        <v>-2820.101415203864</v>
+        <v>188665.8358090796</v>
       </c>
       <c r="E12">
-        <v>100762.5465009056</v>
+        <v>386215.556131683</v>
       </c>
       <c r="F12">
-        <v>74619.37445955064</v>
+        <v>272293.7709899102</v>
       </c>
       <c r="G12">
-        <v>-3469.947666282956</v>
+        <v>136428.7570856202</v>
       </c>
       <c r="H12">
-        <v>173288.7035031838</v>
+        <v>434038.8069771477</v>
       </c>
       <c r="I12">
-        <v>741788806.7953339</v>
+        <v>16444280651.44344</v>
       </c>
       <c r="J12">
-        <v>-41757241.65492348</v>
+        <v>10509064386.23731</v>
       </c>
       <c r="K12">
-        <v>1491991026.038915</v>
+        <v>21512978907.64698</v>
       </c>
       <c r="L12">
-        <v>9924376803.120235</v>
+        <v>36215071541.65805</v>
       </c>
       <c r="M12">
-        <v>-461503039.6156332</v>
+        <v>18145024692.38748</v>
       </c>
       <c r="N12">
-        <v>23047397565.92344</v>
+        <v>57727161327.96065</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>mort</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -966,46 +966,46 @@
         </is>
       </c>
       <c r="C13">
-        <v>45191.80900532119</v>
+        <v>201898.9614152511</v>
       </c>
       <c r="D13">
-        <v>32037.13558413629</v>
+        <v>129081.3530391022</v>
       </c>
       <c r="E13">
-        <v>56868.77249776782</v>
+        <v>264183.1502992219</v>
       </c>
       <c r="F13">
-        <v>41571.96095689302</v>
+        <v>2313109.080426413</v>
       </c>
       <c r="G13">
-        <v>23318.47963966112</v>
+        <v>1476484.828920645</v>
       </c>
       <c r="H13">
-        <v>63409.8285206935</v>
+        <v>3024652.489304188</v>
       </c>
       <c r="I13">
-        <v>2517274145.214404</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>1784532526.307562</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>3167704365.670654</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>5529070807.266772</v>
+        <v>307643507696.713</v>
       </c>
       <c r="M13">
-        <v>3101357792.074929</v>
+        <v>196372482246.4458</v>
       </c>
       <c r="N13">
-        <v>8433507193.252236</v>
+        <v>402278781077.457</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1014,46 +1014,46 @@
         </is>
       </c>
       <c r="C14">
-        <v>12934.41118488275</v>
+        <v>92750.80380844926</v>
       </c>
       <c r="D14">
-        <v>9415.914686372307</v>
+        <v>59189.9430535955</v>
       </c>
       <c r="E14">
-        <v>15975.9909843251</v>
+        <v>121266.0435217691</v>
       </c>
       <c r="F14">
-        <v>20869.11905234802</v>
+        <v>177570.4394420838</v>
       </c>
       <c r="G14">
-        <v>12194.97151108709</v>
+        <v>84299.88584708239</v>
       </c>
       <c r="H14">
-        <v>29325.37992707074</v>
+        <v>294730.709853746</v>
       </c>
       <c r="I14">
-        <v>217802549.9422402</v>
+        <v>6974953197.199179</v>
       </c>
       <c r="J14">
-        <v>158554587.4038234</v>
+        <v>4451142907.57344</v>
       </c>
       <c r="K14">
-        <v>269019712.1850498</v>
+        <v>9119327738.880478</v>
       </c>
       <c r="L14">
-        <v>2775592833.962287</v>
+        <v>23616868445.79714</v>
       </c>
       <c r="M14">
-        <v>1621931210.974584</v>
+        <v>11211884817.66196</v>
       </c>
       <c r="N14">
-        <v>3900275530.300409</v>
+        <v>39199184410.54822</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>11651.00916021903</v>
+        <v>59268.65431980818</v>
       </c>
       <c r="D15">
-        <v>151.672710025489</v>
+        <v>37920.11192277947</v>
       </c>
       <c r="E15">
-        <v>20426.8771942701</v>
+        <v>77573.44560748234</v>
       </c>
       <c r="F15">
-        <v>22402.96693453318</v>
+        <v>96530.22494881996</v>
       </c>
       <c r="G15">
-        <v>224.4999565980998</v>
+        <v>49444.78411568752</v>
       </c>
       <c r="H15">
-        <v>49826.12609743083</v>
+        <v>143815.9424640743</v>
       </c>
       <c r="I15">
-        <v>876167539.8576332</v>
+        <v>998024870.0912468</v>
       </c>
       <c r="J15">
-        <v>11405939.46662686</v>
+        <v>638536764.6676838</v>
       </c>
       <c r="K15">
-        <v>1536121591.886309</v>
+        <v>1306259250.584385</v>
       </c>
       <c r="L15">
-        <v>2979594602.292913</v>
+        <v>12838519918.19305</v>
       </c>
       <c r="M15">
-        <v>29858494.22754727</v>
+        <v>6576156287.38644</v>
       </c>
       <c r="N15">
-        <v>6626874770.958301</v>
+        <v>19127520347.72188</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>360725.7794256359</v>
+        <v>2523951.338870222</v>
       </c>
       <c r="D16">
-        <v>235681.2757739804</v>
+        <v>1617167.658452089</v>
       </c>
       <c r="E16">
-        <v>472127.8975950318</v>
+        <v>3305865.962827697</v>
       </c>
       <c r="F16">
-        <v>1322779.76793264</v>
+        <v>7231405.129795966</v>
       </c>
       <c r="G16">
-        <v>807323.9331739176</v>
+        <v>3558029.79711109</v>
       </c>
       <c r="H16">
-        <v>2046306.942823823</v>
+        <v>12227351.12085755</v>
       </c>
       <c r="I16">
-        <v>3732821445.353777</v>
+        <v>32999329825.94008</v>
       </c>
       <c r="J16">
-        <v>1600831949.937253</v>
+        <v>21138050889.27472</v>
       </c>
       <c r="K16">
-        <v>5606158752.723078</v>
+        <v>43230687945.89658</v>
       </c>
       <c r="L16">
-        <v>175929709135.0412</v>
+        <v>961776882262.8634</v>
       </c>
       <c r="M16">
-        <v>107374083112.131</v>
+        <v>473217963015.775</v>
       </c>
       <c r="N16">
-        <v>272158823395.5685</v>
+        <v>1626237699074.054</v>
       </c>
     </row>
     <row r="17">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>210437.8905157994</v>
+        <v>1165083.994412385</v>
       </c>
       <c r="D17">
-        <v>161461.0198051779</v>
+        <v>746527.0937947494</v>
       </c>
       <c r="E17">
-        <v>251275.0084889801</v>
+        <v>1525664.379200442</v>
       </c>
       <c r="F17">
-        <v>619284.1380716657</v>
+        <v>3417349.805180832</v>
       </c>
       <c r="G17">
-        <v>294078.6896811156</v>
+        <v>1354642.021140593</v>
       </c>
       <c r="H17">
-        <v>1129681.966296552</v>
+        <v>6836311.544284264</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,19 +1185,19 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>82364790363.53154</v>
+        <v>454507524089.0507</v>
       </c>
       <c r="M17">
-        <v>39112465727.58837</v>
+        <v>180167388811.6988</v>
       </c>
       <c r="N17">
-        <v>150247701517.4414</v>
+        <v>909229435389.807</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mort</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1206,46 +1206,46 @@
         </is>
       </c>
       <c r="C18">
-        <v>47782.13973022057</v>
+        <v>802272.9373560263</v>
       </c>
       <c r="D18">
-        <v>41037.36682772607</v>
+        <v>513927.6107471767</v>
       </c>
       <c r="E18">
-        <v>54080.52586579061</v>
+        <v>1050675.046540066</v>
       </c>
       <c r="F18">
-        <v>561419.5865093252</v>
+        <v>1253133.438424966</v>
       </c>
       <c r="G18">
-        <v>484747.8274755173</v>
+        <v>635183.0583431993</v>
       </c>
       <c r="H18">
-        <v>633176.436107637</v>
+        <v>1894205.34855547</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>11879255383.43076</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>7609726132.333516</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>15557345414.11877</v>
       </c>
       <c r="L18">
-        <v>74668805005.74025</v>
+        <v>166666747310.5204</v>
       </c>
       <c r="M18">
-        <v>64471461054.2438</v>
+        <v>84479346759.64551</v>
       </c>
       <c r="N18">
-        <v>84212466002.31572</v>
+        <v>251929311357.8776</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1254,46 +1254,46 @@
         </is>
       </c>
       <c r="C19">
-        <v>42258.68551835822</v>
+        <v>249500.4992293646</v>
       </c>
       <c r="D19">
-        <v>-1833.904308357241</v>
+        <v>159859.5691935084</v>
       </c>
       <c r="E19">
-        <v>85089.41198710834</v>
+        <v>327021.0509900748</v>
       </c>
       <c r="F19">
-        <v>66415.44239852291</v>
+        <v>237849.1381871999</v>
       </c>
       <c r="G19">
-        <v>-2385.865331223808</v>
+        <v>119498.1930921545</v>
       </c>
       <c r="H19">
-        <v>154411.6513993545</v>
+        <v>379693.0374372147</v>
       </c>
       <c r="I19">
-        <v>625724356.4703307</v>
+        <v>13897676808.07413</v>
       </c>
       <c r="J19">
-        <v>-27154621.09384565</v>
+        <v>8904497723.216824</v>
       </c>
       <c r="K19">
-        <v>1259918923.293112</v>
+        <v>18215726582.24927</v>
       </c>
       <c r="L19">
-        <v>8833253839.003548</v>
+        <v>31633935378.89759</v>
       </c>
       <c r="M19">
-        <v>-317320089.0527664</v>
+        <v>15893259681.25654</v>
       </c>
       <c r="N19">
-        <v>20536749636.11415</v>
+        <v>50499173979.14955</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>mort</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1302,46 +1302,46 @@
         </is>
       </c>
       <c r="C20">
-        <v>38574.49935164709</v>
+        <v>171479.5287448698</v>
       </c>
       <c r="D20">
-        <v>26586.4373874868</v>
+        <v>109965.9427141158</v>
       </c>
       <c r="E20">
-        <v>49448.46981781944</v>
+        <v>224820.3746579708</v>
       </c>
       <c r="F20">
-        <v>36652.39340397252</v>
+        <v>2069445.607881794</v>
       </c>
       <c r="G20">
-        <v>20047.59142403122</v>
+        <v>1324810.078433071</v>
       </c>
       <c r="H20">
-        <v>56849.12169021871</v>
+        <v>2709543.880419902</v>
       </c>
       <c r="I20">
-        <v>2148676762.885436</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>1480917735.357788</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>2754378665.792172</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>4874768322.728345</v>
+        <v>275236265848.2786</v>
       </c>
       <c r="M20">
-        <v>2666329659.396152</v>
+        <v>176199740431.5984</v>
       </c>
       <c r="N20">
-        <v>7560933184.799088</v>
+        <v>360369336095.847</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1350,46 +1350,46 @@
         </is>
       </c>
       <c r="C21">
-        <v>11503.68703349809</v>
+        <v>84623.33546324586</v>
       </c>
       <c r="D21">
-        <v>8342.797891455983</v>
+        <v>54157.31808100463</v>
       </c>
       <c r="E21">
-        <v>14259.34811659477</v>
+        <v>110784.0094240234</v>
       </c>
       <c r="F21">
-        <v>18364.80374344331</v>
+        <v>171444.5677254441</v>
       </c>
       <c r="G21">
-        <v>10699.91313891912</v>
+        <v>81664.2078112544</v>
       </c>
       <c r="H21">
-        <v>25879.40465696505</v>
+        <v>284913.8805347253</v>
       </c>
       <c r="I21">
-        <v>193710585.9570748</v>
+        <v>6363759450.17153</v>
       </c>
       <c r="J21">
-        <v>140484373.6942273</v>
+        <v>4072684477.009662</v>
       </c>
       <c r="K21">
-        <v>240113162.9353394</v>
+        <v>8331068292.695953</v>
       </c>
       <c r="L21">
-        <v>2442518897.877961</v>
+        <v>22802127507.48407</v>
       </c>
       <c r="M21">
-        <v>1423088447.476243</v>
+        <v>10861339638.89684</v>
       </c>
       <c r="N21">
-        <v>3441960819.376352</v>
+        <v>37893546111.11846</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>10168.87727611247</v>
+        <v>50991.04366433024</v>
       </c>
       <c r="D22">
-        <v>87.55817049086444</v>
+        <v>32730.12392153444</v>
       </c>
       <c r="E22">
-        <v>17975.13331873855</v>
+        <v>66901.10201511951</v>
       </c>
       <c r="F22">
-        <v>20643.40380571091</v>
+        <v>82182.57239572945</v>
       </c>
       <c r="G22">
-        <v>135.7767855582018</v>
+        <v>42232.23829081892</v>
       </c>
       <c r="H22">
-        <v>46308.36267309635</v>
+        <v>122683.4296259731</v>
       </c>
       <c r="I22">
-        <v>764709740.0409356</v>
+        <v>858638184.2636615</v>
       </c>
       <c r="J22">
-        <v>6584461.979083515</v>
+        <v>551142556.7147171</v>
       </c>
       <c r="K22">
-        <v>1351748000.702454</v>
+        <v>1126547656.832593</v>
       </c>
       <c r="L22">
-        <v>2745572706.159552</v>
+        <v>10930282128.63202</v>
       </c>
       <c r="M22">
-        <v>18058312.47924083</v>
+        <v>5616887692.678916</v>
       </c>
       <c r="N22">
-        <v>6159012235.521814</v>
+        <v>16316896140.25442</v>
       </c>
     </row>
   </sheetData>
